--- a/evaluations/classification/classification_results_grid_search_final_new.xlsx
+++ b/evaluations/classification/classification_results_grid_search_final_new.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y16"/>
+  <dimension ref="A1:Y39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -642,9 +642,13 @@
       <c r="C3" t="n">
         <v>174</v>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
       <c r="E3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" t="b">
         <v>0</v>
@@ -664,9 +668,13 @@
         <v>128</v>
       </c>
       <c r="K3" t="b">
-        <v>0</v>
-      </c>
-      <c r="L3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>RANSAC</t>
+        </is>
+      </c>
       <c r="M3" t="n">
         <v>0.35</v>
       </c>
@@ -686,24 +694,28 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0.09</v>
+        <v>8.01</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9899</v>
+        <v>0.976</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9912</v>
+        <v>0.9937</v>
       </c>
       <c r="V3" t="n">
-        <v>0.9893999999999999</v>
+        <v>0.9749</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
           <t>WildlifeReID10k</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
+      <c r="X3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -717,12 +729,16 @@
       <c r="C4" t="n">
         <v>174</v>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
       <c r="E4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4" t="b">
         <v>1</v>
@@ -739,9 +755,13 @@
         <v>128</v>
       </c>
       <c r="K4" t="b">
-        <v>0</v>
-      </c>
-      <c r="L4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>RANSAC</t>
+        </is>
+      </c>
       <c r="M4" t="n">
         <v>0.35</v>
       </c>
@@ -761,24 +781,28 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2</v>
+        <v>7.88</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5347</v>
+        <v>0.8865</v>
       </c>
       <c r="U4" t="n">
-        <v>0.6974</v>
+        <v>0.9382</v>
       </c>
       <c r="V4" t="n">
-        <v>0.5125999999999999</v>
+        <v>0.8776</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
           <t>WildlifeReID10k</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
+      <c r="X4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -792,12 +816,16 @@
       <c r="C5" t="n">
         <v>174</v>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
       <c r="E5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" t="b">
         <v>1</v>
@@ -814,9 +842,13 @@
         <v>128</v>
       </c>
       <c r="K5" t="b">
-        <v>0</v>
-      </c>
-      <c r="L5" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>RANSAC</t>
+        </is>
+      </c>
       <c r="M5" t="n">
         <v>0.35</v>
       </c>
@@ -836,24 +868,28 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0.09</v>
+        <v>8.01</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7869</v>
+        <v>0.9912</v>
       </c>
       <c r="U5" t="n">
-        <v>0.8386</v>
+        <v>0.9912</v>
       </c>
       <c r="V5" t="n">
-        <v>0.7869</v>
+        <v>0.9908</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
           <t>WildlifeReID10k</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
+      <c r="X5" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -879,9 +915,13 @@
         <v>0</v>
       </c>
       <c r="G6" t="b">
-        <v>0</v>
-      </c>
-      <c r="H6" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>resnet50</t>
+        </is>
+      </c>
       <c r="I6" t="n">
         <v>256</v>
       </c>
@@ -889,9 +929,13 @@
         <v>128</v>
       </c>
       <c r="K6" t="b">
-        <v>0</v>
-      </c>
-      <c r="L6" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>RANSAC</t>
+        </is>
+      </c>
       <c r="M6" t="n">
         <v>0.35</v>
       </c>
@@ -911,24 +955,28 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>8.789999999999999</v>
+        <v>7.74</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8827</v>
+        <v>0.8348</v>
       </c>
       <c r="U6" t="n">
-        <v>0.9281</v>
+        <v>0.8979</v>
       </c>
       <c r="V6" t="n">
-        <v>0.8718</v>
+        <v>0.821</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
           <t>WildlifeReID10k</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
+      <c r="X6" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -954,9 +1002,13 @@
         <v>0</v>
       </c>
       <c r="G7" t="b">
-        <v>0</v>
-      </c>
-      <c r="H7" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>resnet50</t>
+        </is>
+      </c>
       <c r="I7" t="n">
         <v>256</v>
       </c>
@@ -990,24 +1042,28 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>7.94</v>
+        <v>9.15</v>
       </c>
       <c r="T7" t="n">
-        <v>0.8953</v>
+        <v>0.8083</v>
       </c>
       <c r="U7" t="n">
-        <v>0.9357</v>
+        <v>0.8764</v>
       </c>
       <c r="V7" t="n">
-        <v>0.8871</v>
+        <v>0.7925</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
           <t>WildlifeReID10k</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
+      <c r="X7" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1030,12 +1086,16 @@
         <v>1</v>
       </c>
       <c r="F8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" t="b">
-        <v>0</v>
-      </c>
-      <c r="H8" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
       <c r="I8" t="n">
         <v>256</v>
       </c>
@@ -1043,9 +1103,13 @@
         <v>128</v>
       </c>
       <c r="K8" t="b">
-        <v>0</v>
-      </c>
-      <c r="L8" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>RANSAC</t>
+        </is>
+      </c>
       <c r="M8" t="n">
         <v>0.35</v>
       </c>
@@ -1065,24 +1129,28 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>6.64</v>
+        <v>8.1</v>
       </c>
       <c r="T8" t="n">
-        <v>0.7924</v>
+        <v>0.9912</v>
       </c>
       <c r="U8" t="n">
-        <v>0.8658</v>
+        <v>0.9912</v>
       </c>
       <c r="V8" t="n">
-        <v>0.7904</v>
+        <v>0.9908</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
           <t>WildlifeReID10k</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr"/>
+      <c r="X8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1105,12 +1173,16 @@
         <v>1</v>
       </c>
       <c r="F9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" t="b">
-        <v>0</v>
-      </c>
-      <c r="H9" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
       <c r="I9" t="n">
         <v>256</v>
       </c>
@@ -1144,24 +1216,28 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>6.48</v>
+        <v>8.06</v>
       </c>
       <c r="T9" t="n">
-        <v>0.8101</v>
+        <v>0.9937</v>
       </c>
       <c r="U9" t="n">
-        <v>0.8722</v>
+        <v>0.995</v>
       </c>
       <c r="V9" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.9935</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
           <t>WildlifeReID10k</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
+      <c r="X9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1175,13 +1251,9 @@
       <c r="C10" t="n">
         <v>174</v>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>ensamble</t>
-        </is>
-      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10" t="b">
         <v>0</v>
@@ -1191,7 +1263,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>resnet50</t>
+          <t>megadescriptor-l-384</t>
         </is>
       </c>
       <c r="I10" t="n">
@@ -1223,28 +1295,24 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>9.31</v>
+        <v>0.09</v>
       </c>
       <c r="T10" t="n">
-        <v>0.8108</v>
+        <v>0.9899</v>
       </c>
       <c r="U10" t="n">
-        <v>0.918</v>
+        <v>0.9912</v>
       </c>
       <c r="V10" t="n">
-        <v>0.7945</v>
+        <v>0.9893999999999999</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
           <t>WildlifeReID10k</t>
         </is>
       </c>
-      <c r="X10" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1</v>
-      </c>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1258,16 +1326,12 @@
       <c r="C11" t="n">
         <v>174</v>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>ensamble</t>
-        </is>
-      </c>
+      <c r="D11" t="inlineStr"/>
       <c r="E11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" t="b">
         <v>1</v>
@@ -1284,13 +1348,9 @@
         <v>128</v>
       </c>
       <c r="K11" t="b">
-        <v>1</v>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>RANSAC</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
         <v>0.35</v>
       </c>
@@ -1310,28 +1370,24 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>8.710000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="T11" t="n">
-        <v>0.8777</v>
+        <v>0.5347</v>
       </c>
       <c r="U11" t="n">
-        <v>0.9319</v>
+        <v>0.6974</v>
       </c>
       <c r="V11" t="n">
-        <v>0.867</v>
+        <v>0.5125999999999999</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
           <t>WildlifeReID10k</t>
         </is>
       </c>
-      <c r="X11" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1</v>
-      </c>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1345,16 +1401,12 @@
       <c r="C12" t="n">
         <v>174</v>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>ensamble</t>
-        </is>
-      </c>
+      <c r="D12" t="inlineStr"/>
       <c r="E12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" t="b">
         <v>1</v>
@@ -1393,28 +1445,24 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>9.630000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="T12" t="n">
-        <v>0.9887</v>
+        <v>0.7869</v>
       </c>
       <c r="U12" t="n">
-        <v>0.9912</v>
+        <v>0.8386</v>
       </c>
       <c r="V12" t="n">
-        <v>0.9872</v>
+        <v>0.7869</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
           <t>WildlifeReID10k</t>
         </is>
       </c>
-      <c r="X12" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1</v>
-      </c>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1440,13 +1488,9 @@
         <v>0</v>
       </c>
       <c r="G13" t="b">
-        <v>1</v>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>megadescriptor-l-384</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="n">
         <v>256</v>
       </c>
@@ -1454,13 +1498,9 @@
         <v>128</v>
       </c>
       <c r="K13" t="b">
-        <v>1</v>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>RANSAC</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="n">
         <v>0.35</v>
       </c>
@@ -1480,28 +1520,24 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>8.710000000000001</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>0.9899</v>
+        <v>0.8827</v>
       </c>
       <c r="U13" t="n">
-        <v>0.9912</v>
+        <v>0.9281</v>
       </c>
       <c r="V13" t="n">
-        <v>0.9893999999999999</v>
+        <v>0.8718</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
           <t>WildlifeReID10k</t>
         </is>
       </c>
-      <c r="X13" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1</v>
-      </c>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1527,13 +1563,9 @@
         <v>0</v>
       </c>
       <c r="G14" t="b">
-        <v>1</v>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>resnet50</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="n">
         <v>256</v>
       </c>
@@ -1541,9 +1573,13 @@
         <v>128</v>
       </c>
       <c r="K14" t="b">
-        <v>0</v>
-      </c>
-      <c r="L14" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>RANSAC</t>
+        </is>
+      </c>
       <c r="M14" t="n">
         <v>0.35</v>
       </c>
@@ -1563,28 +1599,24 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>9.66</v>
+        <v>7.94</v>
       </c>
       <c r="T14" t="n">
-        <v>0.8789</v>
+        <v>0.8953</v>
       </c>
       <c r="U14" t="n">
-        <v>0.9332</v>
+        <v>0.9357</v>
       </c>
       <c r="V14" t="n">
-        <v>0.8692</v>
+        <v>0.8871</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
           <t>WildlifeReID10k</t>
         </is>
       </c>
-      <c r="X14" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>2</v>
-      </c>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1624,13 +1656,9 @@
         <v>128</v>
       </c>
       <c r="K15" t="b">
-        <v>1</v>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>RANSAC</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L15" t="inlineStr"/>
       <c r="M15" t="n">
         <v>0.35</v>
       </c>
@@ -1650,16 +1678,16 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>8.9</v>
+        <v>9.31</v>
       </c>
       <c r="T15" t="n">
-        <v>0.889</v>
+        <v>0.8108</v>
       </c>
       <c r="U15" t="n">
-        <v>0.9332</v>
+        <v>0.918</v>
       </c>
       <c r="V15" t="n">
-        <v>0.8812</v>
+        <v>0.7945</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
@@ -1670,7 +1698,7 @@
         <v>1</v>
       </c>
       <c r="Y15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1694,16 +1722,12 @@
         <v>1</v>
       </c>
       <c r="F16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16" t="b">
-        <v>1</v>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>megadescriptor-l-384</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="n">
         <v>256</v>
       </c>
@@ -1711,11 +1735,11 @@
         <v>128</v>
       </c>
       <c r="K16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>RANSAC</t>
         </is>
       </c>
       <c r="M16" t="n">
@@ -1737,27 +1761,1956 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
+        <v>6.48</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0.8101</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0.8722</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0.8070000000000001</v>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ATRW</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>4325</v>
+      </c>
+      <c r="C17" t="n">
+        <v>174</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="E17" t="b">
+        <v>1</v>
+      </c>
+      <c r="F17" t="b">
+        <v>0</v>
+      </c>
+      <c r="G17" t="b">
+        <v>1</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>256</v>
+      </c>
+      <c r="J17" t="n">
+        <v>128</v>
+      </c>
+      <c r="K17" t="b">
+        <v>1</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>RANSAC</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="N17" t="n">
+        <v>10</v>
+      </c>
+      <c r="O17" t="n">
+        <v>10</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>5000</v>
+      </c>
+      <c r="R17" t="b">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>8.01</v>
+      </c>
+      <c r="T17" t="n">
+        <v>0.9912</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0.9912</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.9908</v>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
+      <c r="X17" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ATRW</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>4325</v>
+      </c>
+      <c r="C18" t="n">
+        <v>174</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="E18" t="b">
+        <v>1</v>
+      </c>
+      <c r="F18" t="b">
+        <v>0</v>
+      </c>
+      <c r="G18" t="b">
+        <v>1</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>resnet50</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>256</v>
+      </c>
+      <c r="J18" t="n">
+        <v>128</v>
+      </c>
+      <c r="K18" t="b">
+        <v>1</v>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>RANSAC</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="N18" t="n">
+        <v>10</v>
+      </c>
+      <c r="O18" t="n">
+        <v>10</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>5000</v>
+      </c>
+      <c r="R18" t="b">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>9.09</v>
+      </c>
+      <c r="T18" t="n">
+        <v>0.8146</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0.8815</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0.8003</v>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
+      <c r="X18" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ATRW</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>4325</v>
+      </c>
+      <c r="C19" t="n">
+        <v>174</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="E19" t="b">
+        <v>1</v>
+      </c>
+      <c r="F19" t="b">
+        <v>1</v>
+      </c>
+      <c r="G19" t="b">
+        <v>0</v>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="n">
+        <v>256</v>
+      </c>
+      <c r="J19" t="n">
+        <v>128</v>
+      </c>
+      <c r="K19" t="b">
+        <v>0</v>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="N19" t="n">
+        <v>10</v>
+      </c>
+      <c r="O19" t="n">
+        <v>10</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>5000</v>
+      </c>
+      <c r="R19" t="b">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>6.64</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0.7924</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0.8658</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0.7904</v>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ATRW</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>4325</v>
+      </c>
+      <c r="C20" t="n">
+        <v>174</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="E20" t="b">
+        <v>1</v>
+      </c>
+      <c r="F20" t="b">
+        <v>0</v>
+      </c>
+      <c r="G20" t="b">
+        <v>1</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>resnet50</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>256</v>
+      </c>
+      <c r="J20" t="n">
+        <v>128</v>
+      </c>
+      <c r="K20" t="b">
+        <v>1</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>RANSAC</t>
+        </is>
+      </c>
+      <c r="M20" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="N20" t="n">
+        <v>10</v>
+      </c>
+      <c r="O20" t="n">
+        <v>10</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>5000</v>
+      </c>
+      <c r="R20" t="b">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>7.96</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0.8953</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0.9395</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0.8869</v>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
+      <c r="X20" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ATRW</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>4325</v>
+      </c>
+      <c r="C21" t="n">
+        <v>174</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="E21" t="b">
+        <v>1</v>
+      </c>
+      <c r="F21" t="b">
+        <v>0</v>
+      </c>
+      <c r="G21" t="b">
+        <v>1</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>256</v>
+      </c>
+      <c r="J21" t="n">
+        <v>128</v>
+      </c>
+      <c r="K21" t="b">
+        <v>1</v>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>RANSAC</t>
+        </is>
+      </c>
+      <c r="M21" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="N21" t="n">
+        <v>10</v>
+      </c>
+      <c r="O21" t="n">
+        <v>10</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>5000</v>
+      </c>
+      <c r="R21" t="b">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>9.27</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0.9332</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0.966</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0.9296</v>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
+      <c r="X21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ATRW</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>4325</v>
+      </c>
+      <c r="C22" t="n">
+        <v>174</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="E22" t="b">
+        <v>1</v>
+      </c>
+      <c r="F22" t="b">
+        <v>0</v>
+      </c>
+      <c r="G22" t="b">
+        <v>1</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>256</v>
+      </c>
+      <c r="J22" t="n">
+        <v>128</v>
+      </c>
+      <c r="K22" t="b">
+        <v>0</v>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="N22" t="n">
+        <v>10</v>
+      </c>
+      <c r="O22" t="n">
+        <v>10</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>5000</v>
+      </c>
+      <c r="R22" t="b">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>8.98</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0.9899</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0.9912</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0.9893999999999999</v>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
+      <c r="X22" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ATRW</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>4325</v>
+      </c>
+      <c r="C23" t="n">
+        <v>174</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="E23" t="b">
+        <v>1</v>
+      </c>
+      <c r="F23" t="b">
+        <v>0</v>
+      </c>
+      <c r="G23" t="b">
+        <v>1</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>resnet50</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>256</v>
+      </c>
+      <c r="J23" t="n">
+        <v>128</v>
+      </c>
+      <c r="K23" t="b">
+        <v>0</v>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="N23" t="n">
+        <v>10</v>
+      </c>
+      <c r="O23" t="n">
+        <v>10</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>5000</v>
+      </c>
+      <c r="R23" t="b">
+        <v>0</v>
+      </c>
+      <c r="S23" t="n">
+        <v>9.35</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0.8537</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0.6888</v>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
+      <c r="X23" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>ATRW</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>4325</v>
+      </c>
+      <c r="C24" t="n">
+        <v>174</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="E24" t="b">
+        <v>1</v>
+      </c>
+      <c r="F24" t="b">
+        <v>0</v>
+      </c>
+      <c r="G24" t="b">
+        <v>1</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>256</v>
+      </c>
+      <c r="J24" t="n">
+        <v>128</v>
+      </c>
+      <c r="K24" t="b">
+        <v>0</v>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="N24" t="n">
+        <v>10</v>
+      </c>
+      <c r="O24" t="n">
+        <v>10</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>5000</v>
+      </c>
+      <c r="R24" t="b">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>8.85</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0.9836</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0.9937</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0.9831</v>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
+      <c r="X24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ATRW</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>4325</v>
+      </c>
+      <c r="C25" t="n">
+        <v>174</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="E25" t="b">
+        <v>1</v>
+      </c>
+      <c r="F25" t="b">
+        <v>0</v>
+      </c>
+      <c r="G25" t="b">
+        <v>1</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>resnet50</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>256</v>
+      </c>
+      <c r="J25" t="n">
+        <v>128</v>
+      </c>
+      <c r="K25" t="b">
+        <v>0</v>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="N25" t="n">
+        <v>10</v>
+      </c>
+      <c r="O25" t="n">
+        <v>10</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>5000</v>
+      </c>
+      <c r="R25" t="b">
+        <v>0</v>
+      </c>
+      <c r="S25" t="n">
+        <v>8.93</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0.8789</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0.9357</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0.8701</v>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
+      <c r="X25" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ATRW</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>4325</v>
+      </c>
+      <c r="C26" t="n">
+        <v>174</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="E26" t="b">
+        <v>1</v>
+      </c>
+      <c r="F26" t="b">
+        <v>0</v>
+      </c>
+      <c r="G26" t="b">
+        <v>1</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>resnet50</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>256</v>
+      </c>
+      <c r="J26" t="n">
+        <v>128</v>
+      </c>
+      <c r="K26" t="b">
+        <v>0</v>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="N26" t="n">
+        <v>10</v>
+      </c>
+      <c r="O26" t="n">
+        <v>10</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>5000</v>
+      </c>
+      <c r="R26" t="b">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0.884</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0.9319</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0.8742</v>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
+      <c r="X26" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ATRW</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>4325</v>
+      </c>
+      <c r="C27" t="n">
+        <v>174</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="E27" t="b">
+        <v>1</v>
+      </c>
+      <c r="F27" t="b">
+        <v>0</v>
+      </c>
+      <c r="G27" t="b">
+        <v>1</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>256</v>
+      </c>
+      <c r="J27" t="n">
+        <v>128</v>
+      </c>
+      <c r="K27" t="b">
+        <v>0</v>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="N27" t="n">
+        <v>10</v>
+      </c>
+      <c r="O27" t="n">
+        <v>10</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>5000</v>
+      </c>
+      <c r="R27" t="b">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0.9899</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0.9912</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0.9893999999999999</v>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
+      <c r="X27" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ATRW</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>4325</v>
+      </c>
+      <c r="C28" t="n">
+        <v>174</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="E28" t="b">
+        <v>1</v>
+      </c>
+      <c r="F28" t="b">
+        <v>0</v>
+      </c>
+      <c r="G28" t="b">
+        <v>1</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>256</v>
+      </c>
+      <c r="J28" t="n">
+        <v>128</v>
+      </c>
+      <c r="K28" t="b">
+        <v>0</v>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="N28" t="n">
+        <v>10</v>
+      </c>
+      <c r="O28" t="n">
+        <v>10</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>5000</v>
+      </c>
+      <c r="R28" t="b">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>8.83</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0.9899</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0.9912</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0.9893999999999999</v>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
+      <c r="X28" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>ATRW</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>4325</v>
+      </c>
+      <c r="C29" t="n">
+        <v>174</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="E29" t="b">
+        <v>1</v>
+      </c>
+      <c r="F29" t="b">
+        <v>1</v>
+      </c>
+      <c r="G29" t="b">
+        <v>1</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>resnet50</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>256</v>
+      </c>
+      <c r="J29" t="n">
+        <v>128</v>
+      </c>
+      <c r="K29" t="b">
+        <v>0</v>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="N29" t="n">
+        <v>10</v>
+      </c>
+      <c r="O29" t="n">
+        <v>10</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>5000</v>
+      </c>
+      <c r="R29" t="b">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>7.62</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0.6948</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0.7793</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0.6847</v>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
+      <c r="X29" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>ATRW</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>4325</v>
+      </c>
+      <c r="C30" t="n">
+        <v>174</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="E30" t="b">
+        <v>1</v>
+      </c>
+      <c r="F30" t="b">
+        <v>0</v>
+      </c>
+      <c r="G30" t="b">
+        <v>1</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>resnet50</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>256</v>
+      </c>
+      <c r="J30" t="n">
+        <v>128</v>
+      </c>
+      <c r="K30" t="b">
+        <v>1</v>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>RANSAC</t>
+        </is>
+      </c>
+      <c r="M30" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="N30" t="n">
+        <v>10</v>
+      </c>
+      <c r="O30" t="n">
+        <v>10</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>5000</v>
+      </c>
+      <c r="R30" t="b">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0.889</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0.9332</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0.8812</v>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
+      <c r="X30" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>ATRW</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>4325</v>
+      </c>
+      <c r="C31" t="n">
+        <v>174</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="E31" t="b">
+        <v>1</v>
+      </c>
+      <c r="F31" t="b">
+        <v>0</v>
+      </c>
+      <c r="G31" t="b">
+        <v>1</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>256</v>
+      </c>
+      <c r="J31" t="n">
+        <v>128</v>
+      </c>
+      <c r="K31" t="b">
+        <v>1</v>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>RANSAC</t>
+        </is>
+      </c>
+      <c r="M31" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="N31" t="n">
+        <v>10</v>
+      </c>
+      <c r="O31" t="n">
+        <v>10</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>5000</v>
+      </c>
+      <c r="R31" t="b">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>8.710000000000001</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0.9899</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0.9912</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0.9893999999999999</v>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
+      <c r="X31" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>ATRW</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>4325</v>
+      </c>
+      <c r="C32" t="n">
+        <v>174</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="E32" t="b">
+        <v>1</v>
+      </c>
+      <c r="F32" t="b">
+        <v>0</v>
+      </c>
+      <c r="G32" t="b">
+        <v>1</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>256</v>
+      </c>
+      <c r="J32" t="n">
+        <v>128</v>
+      </c>
+      <c r="K32" t="b">
+        <v>0</v>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="N32" t="n">
+        <v>10</v>
+      </c>
+      <c r="O32" t="n">
+        <v>10</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>5000</v>
+      </c>
+      <c r="R32" t="b">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>9.630000000000001</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0.9887</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0.9912</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0.9872</v>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
+      <c r="X32" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>ATRW</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>4325</v>
+      </c>
+      <c r="C33" t="n">
+        <v>174</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="E33" t="b">
+        <v>1</v>
+      </c>
+      <c r="F33" t="b">
+        <v>0</v>
+      </c>
+      <c r="G33" t="b">
+        <v>1</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>resnet50</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>256</v>
+      </c>
+      <c r="J33" t="n">
+        <v>128</v>
+      </c>
+      <c r="K33" t="b">
+        <v>1</v>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>RANSAC</t>
+        </is>
+      </c>
+      <c r="M33" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="N33" t="n">
+        <v>10</v>
+      </c>
+      <c r="O33" t="n">
+        <v>10</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>5000</v>
+      </c>
+      <c r="R33" t="b">
+        <v>0</v>
+      </c>
+      <c r="S33" t="n">
+        <v>8.710000000000001</v>
+      </c>
+      <c r="T33" t="n">
+        <v>0.8777</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0.9319</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0.867</v>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
+      <c r="X33" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>ATRW</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>4325</v>
+      </c>
+      <c r="C34" t="n">
+        <v>174</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="E34" t="b">
+        <v>1</v>
+      </c>
+      <c r="F34" t="b">
+        <v>0</v>
+      </c>
+      <c r="G34" t="b">
+        <v>1</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>resnet50</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>256</v>
+      </c>
+      <c r="J34" t="n">
+        <v>128</v>
+      </c>
+      <c r="K34" t="b">
+        <v>0</v>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="N34" t="n">
+        <v>10</v>
+      </c>
+      <c r="O34" t="n">
+        <v>10</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>5000</v>
+      </c>
+      <c r="R34" t="b">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>8.81</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0.7415</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0.8714</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0.7196</v>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
+      <c r="X34" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>ATRW</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>4325</v>
+      </c>
+      <c r="C35" t="n">
+        <v>174</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="E35" t="b">
+        <v>1</v>
+      </c>
+      <c r="F35" t="b">
+        <v>0</v>
+      </c>
+      <c r="G35" t="b">
+        <v>1</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>256</v>
+      </c>
+      <c r="J35" t="n">
+        <v>128</v>
+      </c>
+      <c r="K35" t="b">
+        <v>0</v>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="N35" t="n">
+        <v>10</v>
+      </c>
+      <c r="O35" t="n">
+        <v>10</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>5000</v>
+      </c>
+      <c r="R35" t="b">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
         <v>9.619999999999999</v>
       </c>
-      <c r="T16" t="n">
+      <c r="T35" t="n">
         <v>0.9899</v>
       </c>
-      <c r="U16" t="n">
+      <c r="U35" t="n">
         <v>0.9937</v>
       </c>
-      <c r="V16" t="n">
+      <c r="V35" t="n">
         <v>0.9893999999999999</v>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="W35" t="inlineStr">
         <is>
           <t>WildlifeReID10k</t>
         </is>
       </c>
-      <c r="X16" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y16" t="n">
+      <c r="X35" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y35" t="n">
         <v>2</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>ATRW</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>4325</v>
+      </c>
+      <c r="C36" t="n">
+        <v>174</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="E36" t="b">
+        <v>1</v>
+      </c>
+      <c r="F36" t="b">
+        <v>0</v>
+      </c>
+      <c r="G36" t="b">
+        <v>1</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>256</v>
+      </c>
+      <c r="J36" t="n">
+        <v>128</v>
+      </c>
+      <c r="K36" t="b">
+        <v>0</v>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="N36" t="n">
+        <v>10</v>
+      </c>
+      <c r="O36" t="n">
+        <v>10</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>5000</v>
+      </c>
+      <c r="R36" t="b">
+        <v>0</v>
+      </c>
+      <c r="S36" t="n">
+        <v>9.56</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0.9268999999999999</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0.9622000000000001</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0.9202</v>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
+      <c r="X36" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>ATRW</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>4325</v>
+      </c>
+      <c r="C37" t="n">
+        <v>174</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="E37" t="b">
+        <v>1</v>
+      </c>
+      <c r="F37" t="b">
+        <v>0</v>
+      </c>
+      <c r="G37" t="b">
+        <v>1</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>resnet50</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>256</v>
+      </c>
+      <c r="J37" t="n">
+        <v>128</v>
+      </c>
+      <c r="K37" t="b">
+        <v>0</v>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="N37" t="n">
+        <v>10</v>
+      </c>
+      <c r="O37" t="n">
+        <v>10</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>5000</v>
+      </c>
+      <c r="R37" t="b">
+        <v>0</v>
+      </c>
+      <c r="S37" t="n">
+        <v>9.119999999999999</v>
+      </c>
+      <c r="T37" t="n">
+        <v>0.6961000000000001</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0.8436</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0.6751</v>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
+      <c r="X37" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>ATRW</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>4325</v>
+      </c>
+      <c r="C38" t="n">
+        <v>174</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="E38" t="b">
+        <v>1</v>
+      </c>
+      <c r="F38" t="b">
+        <v>0</v>
+      </c>
+      <c r="G38" t="b">
+        <v>1</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>resnet50</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>256</v>
+      </c>
+      <c r="J38" t="n">
+        <v>128</v>
+      </c>
+      <c r="K38" t="b">
+        <v>0</v>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="N38" t="n">
+        <v>10</v>
+      </c>
+      <c r="O38" t="n">
+        <v>10</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>5000</v>
+      </c>
+      <c r="R38" t="b">
+        <v>0</v>
+      </c>
+      <c r="S38" t="n">
+        <v>9.66</v>
+      </c>
+      <c r="T38" t="n">
+        <v>0.8789</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0.9332</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0.8692</v>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
+      <c r="X38" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>ATRW</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>4325</v>
+      </c>
+      <c r="C39" t="n">
+        <v>174</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="E39" t="b">
+        <v>1</v>
+      </c>
+      <c r="F39" t="b">
+        <v>1</v>
+      </c>
+      <c r="G39" t="b">
+        <v>1</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>resnet50</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>256</v>
+      </c>
+      <c r="J39" t="n">
+        <v>128</v>
+      </c>
+      <c r="K39" t="b">
+        <v>1</v>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>RANSAC</t>
+        </is>
+      </c>
+      <c r="M39" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="N39" t="n">
+        <v>10</v>
+      </c>
+      <c r="O39" t="n">
+        <v>10</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>5000</v>
+      </c>
+      <c r="R39" t="b">
+        <v>0</v>
+      </c>
+      <c r="S39" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="T39" t="n">
+        <v>0.7579</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0.8108</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0.7494</v>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
+      <c r="X39" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/evaluations/classification/classification_results_grid_search_final_new.xlsx
+++ b/evaluations/classification/classification_results_grid_search_final_new.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y39"/>
+  <dimension ref="A1:Y41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -658,7 +658,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>megadescriptor-l-384</t>
+          <t>resnet50</t>
         </is>
       </c>
       <c r="I3" t="n">
@@ -694,16 +694,16 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>8.01</v>
+        <v>7.88</v>
       </c>
       <c r="T3" t="n">
-        <v>0.976</v>
+        <v>0.8865</v>
       </c>
       <c r="U3" t="n">
-        <v>0.9937</v>
+        <v>0.9382</v>
       </c>
       <c r="V3" t="n">
-        <v>0.9749</v>
+        <v>0.8776</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>resnet50</t>
+          <t>megadescriptor-l-384</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -781,16 +781,16 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>7.88</v>
+        <v>8.01</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8865</v>
+        <v>0.9912</v>
       </c>
       <c r="U4" t="n">
-        <v>0.9382</v>
+        <v>0.9912</v>
       </c>
       <c r="V4" t="n">
-        <v>0.8776</v>
+        <v>0.9908</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -798,10 +798,10 @@
         </is>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -832,7 +832,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>megadescriptor-l-384</t>
+          <t>resnet50</t>
         </is>
       </c>
       <c r="I5" t="n">
@@ -868,16 +868,16 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>8.01</v>
+        <v>7.74</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9912</v>
+        <v>0.8348</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9912</v>
+        <v>0.8979</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9908</v>
+        <v>0.821</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -955,16 +955,16 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>7.74</v>
+        <v>9.15</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8348</v>
+        <v>0.8083</v>
       </c>
       <c r="U6" t="n">
-        <v>0.8979</v>
+        <v>0.8764</v>
       </c>
       <c r="V6" t="n">
-        <v>0.821</v>
+        <v>0.7925</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -972,10 +972,10 @@
         </is>
       </c>
       <c r="X6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y6" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="7">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>resnet50</t>
+          <t>megadescriptor-l-384</t>
         </is>
       </c>
       <c r="I7" t="n">
@@ -1042,16 +1042,16 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>9.15</v>
+        <v>8.1</v>
       </c>
       <c r="T7" t="n">
-        <v>0.8083</v>
+        <v>0.9912</v>
       </c>
       <c r="U7" t="n">
-        <v>0.8764</v>
+        <v>0.9912</v>
       </c>
       <c r="V7" t="n">
-        <v>0.7925</v>
+        <v>0.9908</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
@@ -1062,7 +1062,7 @@
         <v>3</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -1129,16 +1129,16 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>8.1</v>
+        <v>8.06</v>
       </c>
       <c r="T8" t="n">
-        <v>0.9912</v>
+        <v>0.9937</v>
       </c>
       <c r="U8" t="n">
-        <v>0.9912</v>
+        <v>0.995</v>
       </c>
       <c r="V8" t="n">
-        <v>0.9908</v>
+        <v>0.9935</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
@@ -1146,10 +1146,10 @@
         </is>
       </c>
       <c r="X8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>megadescriptor-l-384</t>
+          <t>resnet50</t>
         </is>
       </c>
       <c r="I9" t="n">
@@ -1216,16 +1216,16 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>8.06</v>
+        <v>7.96</v>
       </c>
       <c r="T9" t="n">
-        <v>0.9937</v>
+        <v>0.8953</v>
       </c>
       <c r="U9" t="n">
-        <v>0.995</v>
+        <v>0.9395</v>
       </c>
       <c r="V9" t="n">
-        <v>0.9935</v>
+        <v>0.8869</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -1233,10 +1233,10 @@
         </is>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -1251,9 +1251,13 @@
       <c r="C10" t="n">
         <v>174</v>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
       <c r="E10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" t="b">
         <v>0</v>
@@ -1273,9 +1277,13 @@
         <v>128</v>
       </c>
       <c r="K10" t="b">
-        <v>0</v>
-      </c>
-      <c r="L10" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>RANSAC</t>
+        </is>
+      </c>
       <c r="M10" t="n">
         <v>0.35</v>
       </c>
@@ -1295,24 +1303,28 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0.09</v>
+        <v>8.01</v>
       </c>
       <c r="T10" t="n">
-        <v>0.9899</v>
+        <v>0.976</v>
       </c>
       <c r="U10" t="n">
-        <v>0.9912</v>
+        <v>0.9937</v>
       </c>
       <c r="V10" t="n">
-        <v>0.9893999999999999</v>
+        <v>0.9749</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
           <t>WildlifeReID10k</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
+      <c r="X10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1331,14 +1343,14 @@
         <v>0</v>
       </c>
       <c r="F11" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" t="b">
         <v>1</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>resnet50</t>
+          <t>megadescriptor-l-384</t>
         </is>
       </c>
       <c r="I11" t="n">
@@ -1370,16 +1382,16 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2</v>
+        <v>0.09</v>
       </c>
       <c r="T11" t="n">
-        <v>0.5347</v>
+        <v>0.9899</v>
       </c>
       <c r="U11" t="n">
-        <v>0.6974</v>
+        <v>0.9912</v>
       </c>
       <c r="V11" t="n">
-        <v>0.5125999999999999</v>
+        <v>0.9893999999999999</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
@@ -1401,21 +1413,21 @@
       <c r="C12" t="n">
         <v>174</v>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
       <c r="E12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" t="b">
-        <v>1</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>megadescriptor-l-384</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="n">
         <v>256</v>
       </c>
@@ -1445,16 +1457,16 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0.09</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>0.7869</v>
+        <v>0.8827</v>
       </c>
       <c r="U12" t="n">
-        <v>0.8386</v>
+        <v>0.9281</v>
       </c>
       <c r="V12" t="n">
-        <v>0.7869</v>
+        <v>0.8718</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
@@ -1498,9 +1510,13 @@
         <v>128</v>
       </c>
       <c r="K13" t="b">
-        <v>0</v>
-      </c>
-      <c r="L13" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>RANSAC</t>
+        </is>
+      </c>
       <c r="M13" t="n">
         <v>0.35</v>
       </c>
@@ -1520,16 +1536,16 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>8.789999999999999</v>
+        <v>7.94</v>
       </c>
       <c r="T13" t="n">
-        <v>0.8827</v>
+        <v>0.8953</v>
       </c>
       <c r="U13" t="n">
-        <v>0.9281</v>
+        <v>0.9357</v>
       </c>
       <c r="V13" t="n">
-        <v>0.8718</v>
+        <v>0.8871</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -1563,9 +1579,13 @@
         <v>0</v>
       </c>
       <c r="G14" t="b">
-        <v>0</v>
-      </c>
-      <c r="H14" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>resnet50</t>
+        </is>
+      </c>
       <c r="I14" t="n">
         <v>256</v>
       </c>
@@ -1573,13 +1593,9 @@
         <v>128</v>
       </c>
       <c r="K14" t="b">
-        <v>1</v>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>RANSAC</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="n">
         <v>0.35</v>
       </c>
@@ -1599,24 +1615,28 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>7.94</v>
+        <v>9.31</v>
       </c>
       <c r="T14" t="n">
-        <v>0.8953</v>
+        <v>0.8108</v>
       </c>
       <c r="U14" t="n">
-        <v>0.9357</v>
+        <v>0.918</v>
       </c>
       <c r="V14" t="n">
-        <v>0.8871</v>
+        <v>0.7945</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
           <t>WildlifeReID10k</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="inlineStr"/>
+      <c r="X14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1639,16 +1659,12 @@
         <v>1</v>
       </c>
       <c r="F15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G15" t="b">
-        <v>1</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>resnet50</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="n">
         <v>256</v>
       </c>
@@ -1656,9 +1672,13 @@
         <v>128</v>
       </c>
       <c r="K15" t="b">
-        <v>0</v>
-      </c>
-      <c r="L15" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>RANSAC</t>
+        </is>
+      </c>
       <c r="M15" t="n">
         <v>0.35</v>
       </c>
@@ -1678,28 +1698,24 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>9.31</v>
+        <v>6.48</v>
       </c>
       <c r="T15" t="n">
-        <v>0.8108</v>
+        <v>0.8101</v>
       </c>
       <c r="U15" t="n">
-        <v>0.918</v>
+        <v>0.8722</v>
       </c>
       <c r="V15" t="n">
-        <v>0.7945</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
           <t>WildlifeReID10k</t>
         </is>
       </c>
-      <c r="X15" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1</v>
-      </c>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1722,12 +1738,16 @@
         <v>1</v>
       </c>
       <c r="F16" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G16" t="b">
-        <v>0</v>
-      </c>
-      <c r="H16" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
       <c r="I16" t="n">
         <v>256</v>
       </c>
@@ -1761,24 +1781,28 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>6.48</v>
+        <v>8.01</v>
       </c>
       <c r="T16" t="n">
-        <v>0.8101</v>
+        <v>0.9912</v>
       </c>
       <c r="U16" t="n">
-        <v>0.8722</v>
+        <v>0.9912</v>
       </c>
       <c r="V16" t="n">
-        <v>0.8070000000000001</v>
+        <v>0.9908</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
           <t>WildlifeReID10k</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr"/>
-      <c r="Y16" t="inlineStr"/>
+      <c r="X16" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1808,7 +1832,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>megadescriptor-l-384</t>
+          <t>resnet50</t>
         </is>
       </c>
       <c r="I17" t="n">
@@ -1844,16 +1868,16 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>8.01</v>
+        <v>9.09</v>
       </c>
       <c r="T17" t="n">
-        <v>0.9912</v>
+        <v>0.8146</v>
       </c>
       <c r="U17" t="n">
-        <v>0.9912</v>
+        <v>0.8815</v>
       </c>
       <c r="V17" t="n">
-        <v>0.9908</v>
+        <v>0.8003</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
@@ -1864,7 +1888,7 @@
         <v>3</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1879,16 +1903,12 @@
       <c r="C18" t="n">
         <v>174</v>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>ensamble</t>
-        </is>
-      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G18" t="b">
         <v>1</v>
@@ -1905,13 +1925,9 @@
         <v>128</v>
       </c>
       <c r="K18" t="b">
-        <v>1</v>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>RANSAC</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="n">
         <v>0.35</v>
       </c>
@@ -1931,28 +1947,24 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>9.09</v>
+        <v>0.2</v>
       </c>
       <c r="T18" t="n">
-        <v>0.8146</v>
+        <v>0.5347</v>
       </c>
       <c r="U18" t="n">
-        <v>0.8815</v>
+        <v>0.6974</v>
       </c>
       <c r="V18" t="n">
-        <v>0.8003</v>
+        <v>0.5125999999999999</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
           <t>WildlifeReID10k</t>
         </is>
       </c>
-      <c r="X18" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1</v>
-      </c>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1966,21 +1978,21 @@
       <c r="C19" t="n">
         <v>174</v>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>ensamble</t>
-        </is>
-      </c>
+      <c r="D19" t="inlineStr"/>
       <c r="E19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F19" t="b">
         <v>1</v>
       </c>
       <c r="G19" t="b">
-        <v>0</v>
-      </c>
-      <c r="H19" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
       <c r="I19" t="n">
         <v>256</v>
       </c>
@@ -2010,16 +2022,16 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>6.64</v>
+        <v>0.09</v>
       </c>
       <c r="T19" t="n">
-        <v>0.7924</v>
+        <v>0.7869</v>
       </c>
       <c r="U19" t="n">
-        <v>0.8658</v>
+        <v>0.8386</v>
       </c>
       <c r="V19" t="n">
-        <v>0.7904</v>
+        <v>0.7869</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
@@ -2050,16 +2062,12 @@
         <v>1</v>
       </c>
       <c r="F20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G20" t="b">
-        <v>1</v>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>resnet50</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="n">
         <v>256</v>
       </c>
@@ -2067,13 +2075,9 @@
         <v>128</v>
       </c>
       <c r="K20" t="b">
-        <v>1</v>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>RANSAC</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L20" t="inlineStr"/>
       <c r="M20" t="n">
         <v>0.35</v>
       </c>
@@ -2093,28 +2097,24 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>7.96</v>
+        <v>6.64</v>
       </c>
       <c r="T20" t="n">
-        <v>0.8953</v>
+        <v>0.7924</v>
       </c>
       <c r="U20" t="n">
-        <v>0.9395</v>
+        <v>0.8658</v>
       </c>
       <c r="V20" t="n">
-        <v>0.8869</v>
+        <v>0.7904</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
           <t>WildlifeReID10k</t>
         </is>
       </c>
-      <c r="X20" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>3</v>
-      </c>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2224,14 +2224,14 @@
         <v>1</v>
       </c>
       <c r="F22" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22" t="b">
         <v>1</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>megadescriptor-l-384</t>
+          <t>resnet50</t>
         </is>
       </c>
       <c r="I22" t="n">
@@ -2241,9 +2241,13 @@
         <v>128</v>
       </c>
       <c r="K22" t="b">
-        <v>0</v>
-      </c>
-      <c r="L22" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>RANSAC</t>
+        </is>
+      </c>
       <c r="M22" t="n">
         <v>0.35</v>
       </c>
@@ -2263,16 +2267,16 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>8.98</v>
+        <v>6.52</v>
       </c>
       <c r="T22" t="n">
-        <v>0.9899</v>
+        <v>0.7579</v>
       </c>
       <c r="U22" t="n">
-        <v>0.9912</v>
+        <v>0.8108</v>
       </c>
       <c r="V22" t="n">
-        <v>0.9893999999999999</v>
+        <v>0.7494</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
@@ -2280,7 +2284,7 @@
         </is>
       </c>
       <c r="X22" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y22" t="n">
         <v>1</v>
@@ -2895,7 +2899,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>resnet50</t>
+          <t>megadescriptor-l-384</t>
         </is>
       </c>
       <c r="I30" t="n">
@@ -2905,13 +2909,9 @@
         <v>128</v>
       </c>
       <c r="K30" t="b">
-        <v>1</v>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>RANSAC</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L30" t="inlineStr"/>
       <c r="M30" t="n">
         <v>0.35</v>
       </c>
@@ -2931,16 +2931,16 @@
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>8.9</v>
+        <v>8.98</v>
       </c>
       <c r="T30" t="n">
-        <v>0.889</v>
+        <v>0.9899</v>
       </c>
       <c r="U30" t="n">
-        <v>0.9332</v>
+        <v>0.9912</v>
       </c>
       <c r="V30" t="n">
-        <v>0.8812</v>
+        <v>0.9893999999999999</v>
       </c>
       <c r="W30" t="inlineStr">
         <is>
@@ -2948,10 +2948,10 @@
         </is>
       </c>
       <c r="X30" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2982,7 +2982,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>megadescriptor-l-384</t>
+          <t>resnet50</t>
         </is>
       </c>
       <c r="I31" t="n">
@@ -3018,16 +3018,16 @@
         <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>8.710000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="T31" t="n">
-        <v>0.9899</v>
+        <v>0.889</v>
       </c>
       <c r="U31" t="n">
-        <v>0.9912</v>
+        <v>0.9332</v>
       </c>
       <c r="V31" t="n">
-        <v>0.9893999999999999</v>
+        <v>0.8812</v>
       </c>
       <c r="W31" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
         <v>1</v>
       </c>
       <c r="Y31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -3647,14 +3647,14 @@
         <v>1</v>
       </c>
       <c r="F39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G39" t="b">
         <v>1</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>resnet50</t>
+          <t>megadescriptor-l-384</t>
         </is>
       </c>
       <c r="I39" t="n">
@@ -3690,16 +3690,16 @@
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>6.52</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="T39" t="n">
-        <v>0.7579</v>
+        <v>0.9899</v>
       </c>
       <c r="U39" t="n">
-        <v>0.8108</v>
+        <v>0.9912</v>
       </c>
       <c r="V39" t="n">
-        <v>0.7494</v>
+        <v>0.9893999999999999</v>
       </c>
       <c r="W39" t="inlineStr">
         <is>
@@ -3710,6 +3710,176 @@
         <v>1</v>
       </c>
       <c r="Y39" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>ATRW</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>4325</v>
+      </c>
+      <c r="C40" t="n">
+        <v>174</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="E40" t="b">
+        <v>1</v>
+      </c>
+      <c r="F40" t="b">
+        <v>1</v>
+      </c>
+      <c r="G40" t="b">
+        <v>1</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>256</v>
+      </c>
+      <c r="J40" t="n">
+        <v>128</v>
+      </c>
+      <c r="K40" t="b">
+        <v>0</v>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="N40" t="n">
+        <v>10</v>
+      </c>
+      <c r="O40" t="n">
+        <v>10</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>5000</v>
+      </c>
+      <c r="R40" t="b">
+        <v>0</v>
+      </c>
+      <c r="S40" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="T40" t="n">
+        <v>0.7982</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0.8714</v>
+      </c>
+      <c r="V40" t="n">
+        <v>0.7985</v>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
+      <c r="X40" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>ATRW</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>4325</v>
+      </c>
+      <c r="C41" t="n">
+        <v>174</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>ensamble</t>
+        </is>
+      </c>
+      <c r="E41" t="b">
+        <v>1</v>
+      </c>
+      <c r="F41" t="b">
+        <v>1</v>
+      </c>
+      <c r="G41" t="b">
+        <v>1</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>megadescriptor-l-384</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>256</v>
+      </c>
+      <c r="J41" t="n">
+        <v>128</v>
+      </c>
+      <c r="K41" t="b">
+        <v>1</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>RANSAC</t>
+        </is>
+      </c>
+      <c r="M41" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="N41" t="n">
+        <v>10</v>
+      </c>
+      <c r="O41" t="n">
+        <v>10</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>5000</v>
+      </c>
+      <c r="R41" t="b">
+        <v>0</v>
+      </c>
+      <c r="S41" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="T41" t="n">
+        <v>0.8272</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0.8739</v>
+      </c>
+      <c r="V41" t="n">
+        <v>0.8285</v>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>WildlifeReID10k</t>
+        </is>
+      </c>
+      <c r="X41" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y41" t="n">
         <v>1</v>
       </c>
     </row>
